--- a/study_case_model/scenario_variables/price_scenarios142.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios142.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.94467843171416</v>
+        <v>33.49592438445312</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.28652908030821</v>
+        <v>27.41472613226755</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.02785819661286</v>
+        <v>28.1564787874727</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.02592454409629</v>
+        <v>25.64829424100743</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26.23213851250383</v>
+        <v>23.52388204820233</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.95782995705602</v>
+        <v>33.01103048488043</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.21612505126224</v>
+        <v>27.24175953966086</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.30714791669144</v>
+        <v>28.48707199231751</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.54366025666712</v>
+        <v>25.81415384218579</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26.02843503822391</v>
+        <v>23.4559479094832</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.73944869967336</v>
+        <v>29.416702360045</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31.85118849175626</v>
+        <v>24.68180530718405</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.59465131632106</v>
+        <v>28.8552953801677</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>33.54476217591498</v>
+        <v>28.37056492355233</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.01123251579619</v>
+        <v>25.11872554310184</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.56415591487671</v>
+        <v>29.59474244477648</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.43385425329991</v>
+        <v>24.56928322813532</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25.28890721107114</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33.16997707357101</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.67132039510937</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28.80549436755692</v>
+        <v>27.12445164247194</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.65088756644332</v>
+        <v>33.12476542513664</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.51352953379907</v>
+        <v>27.65285208666192</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.919564783438</v>
+        <v>26.50596245049548</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.64033555083007</v>
+        <v>29.44524709129028</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.37440282324375</v>
+        <v>27.62469473362441</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.73478317690562</v>
+        <v>33.16248136481905</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24.91200391956342</v>
+        <v>28.24281772469002</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31.14211396146476</v>
+        <v>26.92388282936668</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.96586047982647</v>
+        <v>29.01949906210304</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.19700641007534</v>
+        <v>25.55156312230822</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.65673064963577</v>
+        <v>29.02446302032637</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34.704149167358</v>
+        <v>22.50485816430386</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.38005121612784</v>
+        <v>26.42249081379442</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>24.09228245291506</v>
+        <v>26.06651176873098</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30.99002677743463</v>
+        <v>25.66880612220536</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.97789999903489</v>
+        <v>28.60970031210099</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>34.74953784854834</v>
+        <v>22.44560835660898</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.25267597038104</v>
+        <v>26.03931382476844</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24.19441479565819</v>
+        <v>26.23573116645012</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/price_scenarios142.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios142.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.49592438445312</v>
+        <v>27.51551466689234</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.41472613226755</v>
+        <v>27.81145630025179</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.1564787874727</v>
+        <v>21.58083915597023</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.64829424100743</v>
+        <v>28.94008052266105</v>
       </c>
     </row>
     <row r="6">
@@ -523,11 +523,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.52388204820233</v>
+        <v>28.00720489645503</v>
       </c>
     </row>
     <row r="7">
@@ -535,15 +535,15 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.01103048488043</v>
+        <v>25.01447174704114</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.24175953966086</v>
+        <v>27.70400346885862</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.48707199231751</v>
+        <v>28.57423408461178</v>
       </c>
     </row>
     <row r="10">
@@ -587,11 +587,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.81415384218579</v>
+        <v>21.33059991720743</v>
       </c>
     </row>
     <row r="11">
@@ -603,11 +603,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23.4559479094832</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="12">
@@ -615,15 +615,15 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.416702360045</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="13">
@@ -631,15 +631,15 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.68180530718405</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="14">
@@ -651,11 +651,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.8552953801677</v>
+        <v>27.12445164247194</v>
       </c>
     </row>
     <row r="15">
@@ -667,11 +667,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.37056492355233</v>
+        <v>33.12476542513664</v>
       </c>
     </row>
     <row r="16">
@@ -683,11 +683,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.11872554310184</v>
+        <v>25.66029609589989</v>
       </c>
     </row>
     <row r="17">
@@ -695,15 +695,15 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.59474244477648</v>
+        <v>24.73889828712912</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24.56928322813532</v>
+        <v>32.73144265246271</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.96212221277759</v>
+        <v>21.52675764849945</v>
       </c>
     </row>
     <row r="20">
@@ -747,11 +747,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.29149387066097</v>
+        <v>27.23542442929922</v>
       </c>
     </row>
     <row r="21">
@@ -763,11 +763,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.10493825262535</v>
+        <v>33.51941514667246</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +775,15 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.12445164247194</v>
+        <v>26.04119582780901</v>
       </c>
     </row>
     <row r="23">
@@ -791,15 +791,15 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.12476542513664</v>
+        <v>24.87688167365211</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.65285208666192</v>
+        <v>32.58497134145912</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.50596245049548</v>
+        <v>21.56536888754603</v>
       </c>
     </row>
     <row r="26">
@@ -843,11 +843,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.44524709129028</v>
+        <v>29.59509787426753</v>
       </c>
     </row>
     <row r="27">
@@ -855,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27.62469473362441</v>
+        <v>22.86517068481368</v>
       </c>
     </row>
     <row r="28">
@@ -871,15 +871,15 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33.16248136481905</v>
+        <v>20.27464152929075</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.24281772469002</v>
+        <v>28.78587458245631</v>
       </c>
     </row>
     <row r="30">
@@ -903,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26.92388282936668</v>
+        <v>32.24344230098109</v>
       </c>
     </row>
     <row r="31">
@@ -919,7 +919,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.01949906210304</v>
+        <v>26.58859601086697</v>
       </c>
     </row>
     <row r="32">
@@ -935,7 +935,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25.55156312230822</v>
+        <v>29.63287084979345</v>
       </c>
     </row>
     <row r="33">
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29.02446302032637</v>
+        <v>22.06546378083905</v>
       </c>
     </row>
     <row r="34">
@@ -967,15 +967,15 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>22.50485816430386</v>
+        <v>20.77433855879205</v>
       </c>
     </row>
     <row r="35">
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.42249081379442</v>
+        <v>28.65317142587766</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +999,15 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26.06651176873098</v>
+        <v>32.69150921423316</v>
       </c>
     </row>
     <row r="37">
@@ -1015,15 +1015,15 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.66880612220536</v>
+        <v>26.53012225190633</v>
       </c>
     </row>
     <row r="38">
@@ -1031,15 +1031,15 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.60970031210099</v>
+        <v>28.43286836223347</v>
       </c>
     </row>
     <row r="39">
@@ -1047,15 +1047,15 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>22.44560835660898</v>
+        <v>27.02064794534943</v>
       </c>
     </row>
     <row r="40">
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26.03931382476844</v>
+        <v>20.41898454388857</v>
       </c>
     </row>
     <row r="41">
@@ -1079,15 +1079,143 @@
         <v>3</v>
       </c>
       <c r="B41" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>26.06986033889535</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>28.46647646866553</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>30.27738708491324</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="n">
         <v>8</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>28.69244689168166</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>27.41996369728102</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20.09171246972934</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25.89929505500652</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>28.50586984771326</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>26.23573116645012</v>
+      <c r="D49" t="n">
+        <v>29.68192534271653</v>
       </c>
     </row>
   </sheetData>
